--- a/artfynd/A 44481-2023 artfynd.xlsx
+++ b/artfynd/A 44481-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44481-2023 artfynd.xlsx
+++ b/artfynd/A 44481-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113109869</v>
       </c>
       <c r="B2" t="n">
-        <v>90105</v>
+        <v>90334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -773,14 +773,18 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>113109896</v>
       </c>
       <c r="B3" t="n">
-        <v>91626</v>
+        <v>91861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,7 +883,11 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,7 +996,7 @@
         <v>113109898</v>
       </c>
       <c r="B5" t="n">
-        <v>91626</v>
+        <v>91861</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1087,7 +1095,11 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,7 +1205,7 @@
         <v>113109893</v>
       </c>
       <c r="B7" t="n">
-        <v>91075</v>
+        <v>91306</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1297,14 +1309,18 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>113109917</v>
       </c>
       <c r="B8" t="n">
-        <v>89012</v>
+        <v>89239</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,7 +1419,11 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1710,7 +1730,7 @@
         <v>113109899</v>
       </c>
       <c r="B12" t="n">
-        <v>91605</v>
+        <v>91840</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1805,14 +1825,18 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>113109900</v>
       </c>
       <c r="B13" t="n">
-        <v>87175</v>
+        <v>87392</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1907,7 +1931,11 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2016,7 +2044,7 @@
         <v>113109870</v>
       </c>
       <c r="B15" t="n">
-        <v>90105</v>
+        <v>90334</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2111,7 +2139,11 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2418,7 +2450,7 @@
         <v>113109845</v>
       </c>
       <c r="B19" t="n">
-        <v>91601</v>
+        <v>91836</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2513,7 +2545,11 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44481-2023 artfynd.xlsx
+++ b/artfynd/A 44481-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113109869</v>
       </c>
       <c r="B2" t="n">
-        <v>90334</v>
+        <v>90351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113109896</v>
       </c>
       <c r="B3" t="n">
-        <v>91861</v>
+        <v>91879</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>113109898</v>
       </c>
       <c r="B5" t="n">
-        <v>91861</v>
+        <v>91879</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>113109893</v>
       </c>
       <c r="B7" t="n">
-        <v>91306</v>
+        <v>91324</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>113109917</v>
       </c>
       <c r="B8" t="n">
-        <v>89239</v>
+        <v>89256</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>113109899</v>
       </c>
       <c r="B12" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>113109900</v>
       </c>
       <c r="B13" t="n">
-        <v>87392</v>
+        <v>87409</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>113109870</v>
       </c>
       <c r="B15" t="n">
-        <v>90334</v>
+        <v>90351</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>113109845</v>
       </c>
       <c r="B19" t="n">
-        <v>91836</v>
+        <v>91854</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
